--- a/data/trans_camb/Hacinamiento_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/Hacinamiento_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 0,96</t>
+          <t>-3,48; 0,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 1,01</t>
+          <t>-3,36; 0,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 1,82</t>
+          <t>-2,73; 1,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 3,24</t>
+          <t>-3,5; 3,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 2,95</t>
+          <t>-3,38; 3,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 0,26</t>
+          <t>-5,1; 0,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 1,04</t>
+          <t>-2,34; 1,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 1,25</t>
+          <t>-2,38; 1,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 0,48</t>
+          <t>-2,99; 0,47</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-77,48; 63,0</t>
+          <t>-80,41; 55,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-78,24; 78,87</t>
+          <t>-76,52; 44,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-61,93; 119,3</t>
+          <t>-65,26; 87,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-54,49; 129,08</t>
+          <t>-56,33; 130,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-56,42; 129,03</t>
+          <t>-56,58; 123,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-82,45; 21,62</t>
+          <t>-79,67; 21,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-55,22; 43,61</t>
+          <t>-54,21; 51,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-54,04; 52,62</t>
+          <t>-54,94; 53,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-62,3; 22,01</t>
+          <t>-62,58; 20,18</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 2,75</t>
+          <t>-1,49; 2,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 3,94</t>
+          <t>-0,72; 3,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 1,58</t>
+          <t>-2,23; 1,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 4,67</t>
+          <t>-2,21; 4,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 2,22</t>
+          <t>-3,86; 2,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,93; -0,84</t>
+          <t>-5,6; -0,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 2,75</t>
+          <t>-0,97; 2,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 2,12</t>
+          <t>-1,5; 2,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,4; -0,23</t>
+          <t>-3,37; -0,15</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-50,74; 303,41</t>
+          <t>-52,93; 297,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-31,02; 518,33</t>
+          <t>-32,7; 434,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-84,47; 258,33</t>
+          <t>-84,86; 218,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-35,83; 163,92</t>
+          <t>-39,22; 159,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-61,28; 79,1</t>
+          <t>-61,99; 68,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-85,81; -21,25</t>
+          <t>-86,37; -18,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-25,94; 121,02</t>
+          <t>-24,67; 123,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-36,25; 98,13</t>
+          <t>-38,47; 103,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-77,28; 3,26</t>
+          <t>-79,59; 0,22</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 2,78</t>
+          <t>-2,2; 2,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 2,67</t>
+          <t>-2,88; 2,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,27; -1,41</t>
+          <t>-6,28; -1,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 3,6</t>
+          <t>-5,67; 3,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 0,62</t>
+          <t>-8,7; 0,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,35; -0,51</t>
+          <t>-9,6; -0,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 2,4</t>
+          <t>-2,26; 2,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 1,08</t>
+          <t>-3,19; 1,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,03; -1,78</t>
+          <t>-6,26; -1,76</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-39,99; 82,04</t>
+          <t>-36,99; 81,2</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-47,43; 75,62</t>
+          <t>-47,87; 56,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-93,57; -34,56</t>
+          <t>-91,72; -31,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-63,93; 107,98</t>
+          <t>-63,92; 109,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-90,56; 54,3</t>
+          <t>-89,82; 54,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-96,72; 17,13</t>
+          <t>-95,49; 30,81</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-34,2; 58,82</t>
+          <t>-34,51; 64,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-52,72; 26,23</t>
+          <t>-51,78; 33,42</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-90,39; -42,61</t>
+          <t>-90,52; -41,93</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 3,35</t>
+          <t>-0,17; 3,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 1,36</t>
+          <t>-1,84; 1,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,7; -0,67</t>
+          <t>-3,59; -0,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 4,81</t>
+          <t>-0,22; 5,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 1,89</t>
+          <t>-2,81; 2,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,03; -2,08</t>
+          <t>-6,13; -2,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 3,4</t>
+          <t>0,1; 3,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 1,02</t>
+          <t>-1,8; 0,96</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,19; -1,58</t>
+          <t>-4,21; -1,65</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 90,77</t>
+          <t>-4,11; 89,7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-42,08; 39,04</t>
+          <t>-36,77; 46,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-69,76; -17,38</t>
+          <t>-70,12; -14,85</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 109,18</t>
+          <t>-4,08; 121,64</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-42,16; 43,31</t>
+          <t>-40,35; 51,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-87,67; -48,01</t>
+          <t>-88,32; -46,73</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,07; 82,1</t>
+          <t>2,94; 81,37</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-31,87; 25,51</t>
+          <t>-32,51; 22,99</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-74,47; -38,86</t>
+          <t>-73,63; -39,13</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 0,52</t>
+          <t>-7,23; 0,42</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,8; -0,62</t>
+          <t>-8,62; -0,63</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-11,66; -3,89</t>
+          <t>-11,67; -4,07</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 1,5</t>
+          <t>-5,09; 1,46</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 0,56</t>
+          <t>-5,32; 1,05</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,86; -3,21</t>
+          <t>-8,92; -3,42</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 0,07</t>
+          <t>-4,79; 0,05</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,67; -0,86</t>
+          <t>-5,83; -0,96</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-8,8; -4,4</t>
+          <t>-9,02; -4,55</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-58,87; 7,91</t>
+          <t>-57,88; 6,5</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-66,76; -6,48</t>
+          <t>-66,96; -5,47</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-87,07; -47,99</t>
+          <t>-87,13; -49,54</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-44,17; 22,86</t>
+          <t>-45,84; 21,96</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-49,56; 10,48</t>
+          <t>-48,83; 13,92</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-79,67; -45,93</t>
+          <t>-79,82; -47,19</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-43,86; 3,99</t>
+          <t>-43,3; 0,62</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-51,18; -10,41</t>
+          <t>-51,74; -12,12</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-79,36; -55,62</t>
+          <t>-79,27; -56,19</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 0,33</t>
+          <t>-7,12; 0,33</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 4,35</t>
+          <t>-3,72; 4,96</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-8,96; -1,76</t>
+          <t>-8,59; -1,74</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 1,23</t>
+          <t>-2,44; 1,15</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,86; -0,28</t>
+          <t>-4,03; -0,61</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 0,54</t>
+          <t>-3,82; 0,28</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 0,6</t>
+          <t>-2,77; 0,59</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,45; -0,11</t>
+          <t>-3,25; 0,11</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-4,47; -0,75</t>
+          <t>-4,63; -0,84</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-79,8; 14,48</t>
+          <t>-78,46; 12,16</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-45,14; 86,69</t>
+          <t>-43,23; 103,35</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -11,38</t>
+          <t>-100,0; -16,41</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-35,57; 29,56</t>
+          <t>-38,48; 24,72</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-60,71; -4,9</t>
+          <t>-61,02; -10,76</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-62,81; 13,27</t>
+          <t>-62,32; 8,2</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-39,31; 12,16</t>
+          <t>-42,2; 12,78</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-51,3; -1,31</t>
+          <t>-48,92; 3,76</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-68,52; -11,03</t>
+          <t>-70,25; -14,67</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 0,97</t>
+          <t>-1,12; 1,06</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 0,62</t>
+          <t>-1,53; 0,53</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,8; -1,82</t>
+          <t>-3,76; -1,88</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 1,47</t>
+          <t>-1,08; 1,38</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,54; -0,25</t>
+          <t>-2,48; -0,26</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,58; -2,54</t>
+          <t>-4,7; -2,63</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 0,89</t>
+          <t>-0,71; 0,93</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,77; -0,16</t>
+          <t>-1,75; -0,16</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-3,89; -2,4</t>
+          <t>-3,84; -2,51</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-21,13; 21,85</t>
+          <t>-21,77; 24,2</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-28,48; 14,07</t>
+          <t>-28,09; 13,42</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-70,26; -41,63</t>
+          <t>-69,21; -41,6</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-15,12; 27,71</t>
+          <t>-15,83; 26,02</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-38,46; -4,72</t>
+          <t>-38,06; -5,52</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-70,15; -47,35</t>
+          <t>-70,76; -46,49</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-13,32; 17,98</t>
+          <t>-12,18; 18,83</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-29,98; -3,09</t>
+          <t>-30,46; -3,44</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-66,45; -47,54</t>
+          <t>-66,56; -49,34</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/Hacinamiento_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/Hacinamiento_R-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,36</t>
+          <t>-0,5</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-2,27</t>
+          <t>-2,19</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,15</t>
+          <t>-1,19</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 0,88</t>
+          <t>-3,37; 0,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 0,78</t>
+          <t>-3,29; 1,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 1,54</t>
+          <t>-2,88; 1,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 3,51</t>
+          <t>-2,97; 3,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 3,03</t>
+          <t>-3,68; 2,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 0,22</t>
+          <t>-4,98; 0,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 1,38</t>
+          <t>-2,31; 1,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 1,3</t>
+          <t>-2,45; 1,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 0,47</t>
+          <t>-2,77; 0,39</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-11,88%</t>
+          <t>-16,35%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-51,59%</t>
+          <t>-49,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-32,29%</t>
+          <t>-33,27%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-80,41; 55,75</t>
+          <t>-78,21; 57,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-76,52; 44,36</t>
+          <t>-79,57; 60,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-65,26; 87,57</t>
+          <t>-65,29; 94,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-56,33; 130,7</t>
+          <t>-49,0; 142,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-56,58; 123,0</t>
+          <t>-61,71; 104,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-79,67; 21,07</t>
+          <t>-76,25; 19,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-54,21; 51,52</t>
+          <t>-52,88; 48,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-54,94; 53,89</t>
+          <t>-53,63; 45,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-62,58; 20,18</t>
+          <t>-60,29; 20,01</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,42</t>
+          <t>-0,07</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,13</t>
+          <t>-2,48</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,79</t>
+          <t>-1,3</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 2,79</t>
+          <t>-1,47; 2,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 3,88</t>
+          <t>-0,62; 3,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 1,48</t>
+          <t>-1,93; 1,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 4,88</t>
+          <t>-2,26; 5,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 2,0</t>
+          <t>-3,91; 2,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,6; -0,8</t>
+          <t>-5,88; -0,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 2,94</t>
+          <t>-1,11; 2,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 2,44</t>
+          <t>-1,62; 2,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,37; -0,15</t>
+          <t>-2,95; 0,32</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-23,04%</t>
+          <t>-3,69%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-66,95%</t>
+          <t>-52,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-55,01%</t>
+          <t>-39,84%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-52,93; 297,35</t>
+          <t>-55,78; 293,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-32,7; 434,31</t>
+          <t>-28,65; 408,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-84,86; 218,33</t>
+          <t>-75,35; 235,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-39,22; 159,41</t>
+          <t>-38,47; 161,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-61,99; 68,37</t>
+          <t>-60,21; 67,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-86,37; -18,99</t>
+          <t>-80,11; -1,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-24,67; 123,8</t>
+          <t>-27,95; 122,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-38,47; 103,79</t>
+          <t>-39,46; 93,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-79,59; 0,22</t>
+          <t>-68,75; 19,04</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-3,45</t>
+          <t>-2,75</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-4,47</t>
+          <t>-3,52</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-3,7</t>
+          <t>-2,92</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 2,87</t>
+          <t>-2,3; 2,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 2,25</t>
+          <t>-3,0; 2,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,28; -1,28</t>
+          <t>-5,03; -0,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 3,78</t>
+          <t>-5,51; 4,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 0,59</t>
+          <t>-8,31; 0,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,6; -0,56</t>
+          <t>-8,9; 0,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 2,42</t>
+          <t>-2,13; 2,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 1,32</t>
+          <t>-3,35; 1,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,26; -1,76</t>
+          <t>-4,87; -0,82</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-69,17%</t>
+          <t>-55,24%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-72,73%</t>
+          <t>-57,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-70,26%</t>
+          <t>-55,46%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-36,99; 81,2</t>
+          <t>-36,74; 79,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-47,87; 56,34</t>
+          <t>-48,06; 65,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-91,72; -31,19</t>
+          <t>-81,38; -5,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-63,92; 109,76</t>
+          <t>-60,91; 151,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-89,82; 54,8</t>
+          <t>-90,22; 52,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-95,49; 30,81</t>
+          <t>-88,75; 57,32</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-34,51; 64,66</t>
+          <t>-32,57; 62,24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-51,78; 33,42</t>
+          <t>-51,96; 33,08</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-90,52; -41,93</t>
+          <t>-76,57; -19,31</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-2,15</t>
+          <t>-1,4</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-3,9</t>
+          <t>-3,03</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,86</t>
+          <t>-2,03</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 3,22</t>
+          <t>-0,54; 3,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 1,56</t>
+          <t>-2,27; 1,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,59; -0,62</t>
+          <t>-3,1; 0,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 5,11</t>
+          <t>-0,7; 4,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 2,06</t>
+          <t>-2,68; 2,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,13; -2,06</t>
+          <t>-5,27; -1,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 3,3</t>
+          <t>0,37; 3,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 0,96</t>
+          <t>-1,87; 0,99</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,21; -1,65</t>
+          <t>-3,44; -0,91</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-48,92%</t>
+          <t>-31,92%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-70,3%</t>
+          <t>-54,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-59,4%</t>
+          <t>-42,12%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 89,7</t>
+          <t>-10,02; 93,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-36,77; 46,06</t>
+          <t>-41,23; 36,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-70,12; -14,85</t>
+          <t>-56,81; 10,36</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 121,64</t>
+          <t>-11,07; 104,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-40,35; 51,24</t>
+          <t>-40,01; 49,76</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-88,32; -46,73</t>
+          <t>-72,24; -25,32</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,94; 81,37</t>
+          <t>6,2; 81,96</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-32,51; 22,99</t>
+          <t>-32,47; 24,37</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-73,63; -39,13</t>
+          <t>-61,03; -20,51</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-7,42</t>
+          <t>-6,77</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-6,08</t>
+          <t>-4,98</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-6,59</t>
+          <t>-5,68</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 0,42</t>
+          <t>-7,79; 0,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,62; -0,63</t>
+          <t>-8,55; -0,83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-11,67; -4,07</t>
+          <t>-11,15; -3,23</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 1,46</t>
+          <t>-4,98; 1,32</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 1,05</t>
+          <t>-5,69; 0,74</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,92; -3,42</t>
+          <t>-7,97; -2,48</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 0,05</t>
+          <t>-4,73; 0,12</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,83; -0,96</t>
+          <t>-5,66; -0,69</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-9,02; -4,55</t>
+          <t>-8,14; -3,67</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-73,9%</t>
+          <t>-67,44%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-67,4%</t>
+          <t>-55,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-69,98%</t>
+          <t>-60,36%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-57,88; 6,5</t>
+          <t>-59,19; 11,11</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-66,96; -5,47</t>
+          <t>-67,38; -9,25</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-87,13; -49,54</t>
+          <t>-83,78; -40,53</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-45,84; 21,96</t>
+          <t>-45,39; 19,4</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-48,83; 13,92</t>
+          <t>-51,26; 10,04</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-79,82; -47,19</t>
+          <t>-71,19; -33,52</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-43,3; 0,62</t>
+          <t>-43,42; 1,66</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-51,74; -12,12</t>
+          <t>-52,65; -9,2</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-79,27; -56,19</t>
+          <t>-71,79; -45,83</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-5,43</t>
+          <t>-5,56</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-2,1</t>
+          <t>-1,46</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-2,83</t>
+          <t>-2,32</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 0,33</t>
+          <t>-6,85; 0,26</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 4,96</t>
+          <t>-3,8; 5,32</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-8,59; -1,74</t>
+          <t>-9,06; -2,42</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 1,15</t>
+          <t>-2,22; 1,4</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,03; -0,61</t>
+          <t>-3,83; -0,48</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 0,28</t>
+          <t>-3,55; 0,93</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 0,59</t>
+          <t>-2,63; 0,55</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 0,11</t>
+          <t>-3,23; 0,04</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-4,63; -0,84</t>
+          <t>-4,06; -0,4</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-79,8%</t>
+          <t>-81,75%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-37,75%</t>
+          <t>-26,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-48,81%</t>
+          <t>-39,9%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-78,46; 12,16</t>
+          <t>-78,43; 9,07</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-43,23; 103,35</t>
+          <t>-43,44; 119,17</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -16,41</t>
+          <t>-100,0; -13,05</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-38,48; 24,72</t>
+          <t>-35,4; 29,41</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-61,02; -10,76</t>
+          <t>-60,85; -9,77</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-62,32; 8,2</t>
+          <t>-56,39; 21,5</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-42,2; 12,78</t>
+          <t>-40,51; 12,64</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-48,92; 3,76</t>
+          <t>-50,05; 2,44</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-70,25; -14,67</t>
+          <t>-62,01; -5,56</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-2,78</t>
+          <t>-2,26</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-3,58</t>
+          <t>-2,8</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-3,18</t>
+          <t>-2,53</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 1,06</t>
+          <t>-1,15; 0,98</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 0,53</t>
+          <t>-1,49; 0,61</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,76; -1,88</t>
+          <t>-3,18; -1,23</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,38</t>
+          <t>-1,02; 1,41</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,48; -0,26</t>
+          <t>-2,64; -0,42</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,7; -2,63</t>
+          <t>-3,86; -1,84</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,93</t>
+          <t>-0,64; 0,86</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,75; -0,16</t>
+          <t>-1,74; -0,24</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-3,84; -2,51</t>
+          <t>-3,21; -1,82</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-57,58%</t>
+          <t>-46,76%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-59,95%</t>
+          <t>-46,99%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-58,88%</t>
+          <t>-46,84%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-21,77; 24,2</t>
+          <t>-21,28; 24,17</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-28,09; 13,42</t>
+          <t>-28,66; 13,57</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-69,21; -41,6</t>
+          <t>-59,21; -28,6</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-15,83; 26,02</t>
+          <t>-15,84; 26,39</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-38,06; -5,52</t>
+          <t>-39,29; -7,56</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-70,76; -46,49</t>
+          <t>-58,32; -33,12</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 18,83</t>
+          <t>-11,04; 17,25</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-30,46; -3,44</t>
+          <t>-30,19; -4,79</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-66,56; -49,34</t>
+          <t>-55,3; -36,6</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/Hacinamiento_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/Hacinamiento_R-Clase-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación</t>
+          <t>Población en cuya vivienda residen dos o más personas por habitación</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
